--- a/trunk/psse_validation/data/AU14GenModel.RAW.xlsx
+++ b/trunk/psse_validation/data/AU14GenModel.RAW.xlsx
@@ -16,21 +16,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="146">
+  <si>
+    <t>names</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>Vm</t>
+  </si>
+  <si>
+    <t>Va(rad)</t>
+  </si>
   <si>
     <t>Va(deg)</t>
   </si>
   <si>
-    <t>Va(rad)</t>
-  </si>
-  <si>
-    <t>Vm</t>
-  </si>
-  <si>
-    <t>names</t>
-  </si>
-  <si>
-    <t>number</t>
+    <t>Vnom</t>
   </si>
   <si>
     <t xml:space="preserve">1_HPSGEN    </t>
@@ -210,10 +213,25 @@
     <t xml:space="preserve">5_SSV275    </t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Q</t>
+    <t>Pf</t>
+  </si>
+  <si>
+    <t>Qf</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>Qt</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>ckt</t>
   </si>
   <si>
     <t>102_217_1</t>
@@ -793,10 +811,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,1185 +830,1365 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>-34.8374348449491</v>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>-0.608027940993362</v>
+        <v>101</v>
       </c>
       <c r="D2">
         <v>1.00000001559023</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="E2">
+        <v>-0.608027940993362</v>
       </c>
       <c r="F2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>-34.8374348449491</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>-30.757284382741</v>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>-0.536815881451062</v>
+        <v>102</v>
       </c>
       <c r="D3">
         <v>1.01191964057205</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="E3">
+        <v>-0.536815881451062</v>
       </c>
       <c r="F3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>-30.757284382741</v>
+      </c>
+      <c r="G3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>6.63765029674239</v>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>0.115848852274133</v>
+        <v>201</v>
       </c>
       <c r="D4">
         <v>1.0000000171342</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
+      <c r="E4">
+        <v>0.115848852274133</v>
       </c>
       <c r="F4">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>6.63765029674239</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>-1.60554643768323</v>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>-0.0280220716312383</v>
+        <v>202</v>
       </c>
       <c r="D5">
         <v>0.999999976754149</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
+      <c r="E5">
+        <v>-0.0280220716312383</v>
       </c>
       <c r="F5">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>-1.60554643768323</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>-5.21436126242005</v>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>-0.0910077724176779</v>
+        <v>203</v>
       </c>
       <c r="D6">
         <v>0.999999999353433</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
+      <c r="E6">
+        <v>-0.0910077724176779</v>
       </c>
       <c r="F6">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>-5.21436126242005</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>204</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="C7">
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>-0.146603216615801</v>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>-0.00255870882396018</v>
+        <v>205</v>
       </c>
       <c r="D8">
         <v>1.04499992081585</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="E8">
+        <v>-0.00255870882396018</v>
       </c>
       <c r="F8">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>-0.146603216615801</v>
+      </c>
+      <c r="G8">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>-0.645859521068433</v>
+      <c r="B9" t="s">
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>-0.0112723751479978</v>
+        <v>206</v>
       </c>
       <c r="D9">
         <v>1.02926225005937</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
+      <c r="E9">
+        <v>-0.0112723751479978</v>
       </c>
       <c r="F9">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>-0.645859521068433</v>
+      </c>
+      <c r="G9">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>-11.4949278484467</v>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>-0.200624338234582</v>
+        <v>207</v>
       </c>
       <c r="D10">
         <v>1.00881218485151</v>
       </c>
-      <c r="E10" t="s">
-        <v>13</v>
+      <c r="E10">
+        <v>-0.200624338234582</v>
       </c>
       <c r="F10">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>-11.4949278484467</v>
+      </c>
+      <c r="G10">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>-12.9559266478539</v>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>-0.226123577651923</v>
+        <v>208</v>
       </c>
       <c r="D11">
         <v>1.0145415304777</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
+      <c r="E11">
+        <v>-0.226123577651923</v>
       </c>
       <c r="F11">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>-12.9559266478539</v>
+      </c>
+      <c r="G11">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>-9.16643667660041</v>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>-0.159984500682244</v>
+        <v>209</v>
       </c>
       <c r="D12">
         <v>1.02004454898237</v>
       </c>
-      <c r="E12" t="s">
-        <v>15</v>
+      <c r="E12">
+        <v>-0.159984500682244</v>
       </c>
       <c r="F12">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>-9.16643667660041</v>
+      </c>
+      <c r="G12">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
-        <v>-11.9899814207275</v>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>-0.209264653044643</v>
+        <v>210</v>
       </c>
       <c r="D13">
         <v>1.05052821094877</v>
       </c>
-      <c r="E13" t="s">
-        <v>16</v>
+      <c r="E13">
+        <v>-0.209264653044643</v>
       </c>
       <c r="F13">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>-11.9899814207275</v>
+      </c>
+      <c r="G13">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>-18.1413675246197</v>
+      <c r="B14" t="s">
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>-0.316626594118987</v>
+        <v>211</v>
       </c>
       <c r="D14">
         <v>1.01130232495022</v>
       </c>
-      <c r="E14" t="s">
-        <v>17</v>
+      <c r="E14">
+        <v>-0.316626594118987</v>
       </c>
       <c r="F14">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>-18.1413675246197</v>
+      </c>
+      <c r="G14">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>-17.8022155757583</v>
+      <c r="B15" t="s">
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>-0.3107072759468</v>
+        <v>212</v>
       </c>
       <c r="D15">
         <v>1.01665686839948</v>
       </c>
-      <c r="E15" t="s">
-        <v>18</v>
+      <c r="E15">
+        <v>-0.3107072759468</v>
       </c>
       <c r="F15">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>-17.8022155757583</v>
+      </c>
+      <c r="G15">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
-        <v>-14.9884063305885</v>
+      <c r="B16" t="s">
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>-0.26159704009553</v>
+        <v>213</v>
       </c>
       <c r="D16">
         <v>1.04309435775572</v>
       </c>
-      <c r="E16" t="s">
-        <v>19</v>
+      <c r="E16">
+        <v>-0.26159704009553</v>
       </c>
       <c r="F16">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>-14.9884063305885</v>
+      </c>
+      <c r="G16">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
-        <v>-17.8606404063888</v>
+      <c r="B17" t="s">
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>-0.311726981606222</v>
+        <v>214</v>
       </c>
       <c r="D17">
         <v>1.03140771284371</v>
       </c>
-      <c r="E17" t="s">
-        <v>20</v>
+      <c r="E17">
+        <v>-0.311726981606222</v>
       </c>
       <c r="F17">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>-17.8606404063888</v>
+      </c>
+      <c r="G17">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
-        <v>-6.98010966591954</v>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>-0.121825895820577</v>
+        <v>215</v>
       </c>
       <c r="D18">
         <v>1.02469460409543</v>
       </c>
-      <c r="E18" t="s">
-        <v>21</v>
+      <c r="E18">
+        <v>-0.121825895820577</v>
       </c>
       <c r="F18">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>-6.98010966591954</v>
+      </c>
+      <c r="G18">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
-        <v>-19.7405653531207</v>
+      <c r="B19" t="s">
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>-0.344537861617073</v>
+        <v>216</v>
       </c>
       <c r="D19">
         <v>1.02452183681098</v>
       </c>
-      <c r="E19" t="s">
-        <v>22</v>
+      <c r="E19">
+        <v>-0.344537861617073</v>
       </c>
       <c r="F19">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>-19.7405653531207</v>
+      </c>
+      <c r="G19">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
-        <v>-23.939656412864</v>
+      <c r="B20" t="s">
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>-0.417825826200652</v>
+        <v>217</v>
       </c>
       <c r="D20">
         <v>1.01231231379274</v>
       </c>
-      <c r="E20" t="s">
-        <v>23</v>
+      <c r="E20">
+        <v>-0.417825826200652</v>
       </c>
       <c r="F20">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>-23.939656412864</v>
+      </c>
+      <c r="G20">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21">
-        <v>-2.63935480851134</v>
+      <c r="B21" t="s">
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>-0.0460654315368673</v>
+        <v>301</v>
       </c>
       <c r="D21">
         <v>0.99999998089222</v>
       </c>
-      <c r="E21" t="s">
-        <v>24</v>
+      <c r="E21">
+        <v>-0.0460654315368673</v>
       </c>
       <c r="F21">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>-2.63935480851134</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>-14.3269336211061</v>
+      <c r="B22" t="s">
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>-0.250052163402975</v>
+        <v>302</v>
       </c>
       <c r="D22">
         <v>1.000000034156</v>
       </c>
-      <c r="E22" t="s">
-        <v>25</v>
+      <c r="E22">
+        <v>-0.250052163402975</v>
       </c>
       <c r="F22">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>-14.3269336211061</v>
+      </c>
+      <c r="G22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23">
-        <v>-9.73415331211641</v>
+      <c r="B23" t="s">
+        <v>27</v>
       </c>
       <c r="C23">
-        <v>-0.169893025190343</v>
+        <v>303</v>
       </c>
       <c r="D23">
         <v>1.02758133650952</v>
       </c>
-      <c r="E23" t="s">
-        <v>26</v>
+      <c r="E23">
+        <v>-0.169893025190343</v>
       </c>
       <c r="F23">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>-9.73415331211641</v>
+      </c>
+      <c r="G23">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24">
-        <v>-21.0969615546991</v>
+      <c r="B24" t="s">
+        <v>28</v>
       </c>
       <c r="C24">
-        <v>-0.368211441296161</v>
+        <v>304</v>
       </c>
       <c r="D24">
         <v>1.00905632313408</v>
       </c>
-      <c r="E24" t="s">
-        <v>27</v>
+      <c r="E24">
+        <v>-0.368211441296161</v>
       </c>
       <c r="F24">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>-21.0969615546991</v>
+      </c>
+      <c r="G24">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25">
-        <v>-22.5877287231432</v>
+      <c r="B25" t="s">
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>-0.394230236766143</v>
+        <v>305</v>
       </c>
       <c r="D25">
         <v>1.01909825417536</v>
       </c>
-      <c r="E25" t="s">
-        <v>28</v>
+      <c r="E25">
+        <v>-0.394230236766143</v>
       </c>
       <c r="F25">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>-22.5877287231432</v>
+      </c>
+      <c r="G25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26">
-        <v>-24.3761725802291</v>
+      <c r="B26" t="s">
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>-0.42544447055936</v>
+        <v>306</v>
       </c>
       <c r="D26">
         <v>1.02055636919399</v>
       </c>
-      <c r="E26" t="s">
-        <v>29</v>
+      <c r="E26">
+        <v>-0.42544447055936</v>
       </c>
       <c r="F26">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>-24.3761725802291</v>
+      </c>
+      <c r="G26">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27">
-        <v>-24.3804481382995</v>
+      <c r="B27" t="s">
+        <v>31</v>
       </c>
       <c r="C27">
-        <v>-0.425519093125048</v>
+        <v>307</v>
       </c>
       <c r="D27">
         <v>1.02321078406023</v>
       </c>
-      <c r="E27" t="s">
-        <v>30</v>
+      <c r="E27">
+        <v>-0.425519093125048</v>
       </c>
       <c r="F27">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>-24.3804481382995</v>
+      </c>
+      <c r="G27">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28">
-        <v>-31.7608558581837</v>
+      <c r="B28" t="s">
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>-0.554331507976634</v>
+        <v>308</v>
       </c>
       <c r="D28">
         <v>1.05048612601267</v>
       </c>
-      <c r="E28" t="s">
-        <v>31</v>
+      <c r="E28">
+        <v>-0.554331507976634</v>
       </c>
       <c r="F28">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>-31.7608558581837</v>
+      </c>
+      <c r="G28">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
-        <v>-29.1693777200613</v>
+      <c r="B29" t="s">
+        <v>33</v>
       </c>
       <c r="C29">
-        <v>-0.509101681972947</v>
+        <v>309</v>
       </c>
       <c r="D29">
         <v>1.02293222467419</v>
       </c>
-      <c r="E29" t="s">
-        <v>32</v>
+      <c r="E29">
+        <v>-0.509101681972947</v>
       </c>
       <c r="F29">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>-29.1693777200613</v>
+      </c>
+      <c r="G29">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30">
-        <v>-21.5710855323953</v>
+      <c r="B30" t="s">
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>-0.376486465769612</v>
+        <v>310</v>
       </c>
       <c r="D30">
         <v>1.01211550659983</v>
       </c>
-      <c r="E30" t="s">
-        <v>33</v>
+      <c r="E30">
+        <v>-0.376486465769612</v>
       </c>
       <c r="F30">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>-21.5710855323953</v>
+      </c>
+      <c r="G30">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31">
-        <v>-25.0416878657902</v>
+      <c r="B31" t="s">
+        <v>35</v>
       </c>
       <c r="C31">
-        <v>-0.437059903514752</v>
+        <v>311</v>
       </c>
       <c r="D31">
         <v>1.03772094823315</v>
       </c>
-      <c r="E31" t="s">
-        <v>34</v>
+      <c r="E31">
+        <v>-0.437059903514752</v>
       </c>
       <c r="F31">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>-25.0416878657902</v>
+      </c>
+      <c r="G31">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32">
-        <v>-20.5126417500473</v>
+      <c r="B32" t="s">
+        <v>36</v>
       </c>
       <c r="C32">
-        <v>-0.358013136820377</v>
+        <v>312</v>
       </c>
       <c r="D32">
         <v>1.03180529796162</v>
       </c>
-      <c r="E32" t="s">
-        <v>35</v>
+      <c r="E32">
+        <v>-0.358013136820377</v>
       </c>
       <c r="F32">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>-20.5126417500473</v>
+      </c>
+      <c r="G32">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33">
-        <v>-28.0344223348302</v>
+      <c r="B33" t="s">
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>-0.489292973637423</v>
+        <v>313</v>
       </c>
       <c r="D33">
         <v>1.0150000133426</v>
       </c>
-      <c r="E33" t="s">
-        <v>36</v>
+      <c r="E33">
+        <v>-0.489292973637423</v>
       </c>
       <c r="F33">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>-28.0344223348302</v>
+      </c>
+      <c r="G33">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34">
-        <v>-26.8630556815019</v>
+      <c r="B34" t="s">
+        <v>38</v>
       </c>
       <c r="C34">
-        <v>-0.468848768788778</v>
+        <v>314</v>
       </c>
       <c r="D34">
         <v>1.01675063453657</v>
       </c>
-      <c r="E34" t="s">
-        <v>37</v>
+      <c r="E34">
+        <v>-0.468848768788778</v>
       </c>
       <c r="F34">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>-26.8630556815019</v>
+      </c>
+      <c r="G34">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35">
-        <v>-33.5133747722992</v>
+      <c r="B35" t="s">
+        <v>39</v>
       </c>
       <c r="C35">
-        <v>-0.584918733231426</v>
+        <v>315</v>
       </c>
       <c r="D35">
         <v>1.0470743306891</v>
       </c>
-      <c r="E35" t="s">
-        <v>38</v>
+      <c r="E35">
+        <v>-0.584918733231426</v>
       </c>
       <c r="F35">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>-33.5133747722992</v>
+      </c>
+      <c r="G35">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36">
-        <v>20.8207686321147</v>
+      <c r="B36" t="s">
+        <v>40</v>
       </c>
       <c r="C36">
-        <v>0.363390965426357</v>
+        <v>401</v>
       </c>
       <c r="D36">
         <v>1.00000001852166</v>
       </c>
-      <c r="E36" t="s">
-        <v>39</v>
+      <c r="E36">
+        <v>0.363390965426357</v>
       </c>
       <c r="F36">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>20.8207686321147</v>
+      </c>
+      <c r="G36">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37">
-        <v>49.8062671416258</v>
+      <c r="B37" t="s">
+        <v>41</v>
       </c>
       <c r="C37">
-        <v>0.869283349749235</v>
+        <v>402</v>
       </c>
       <c r="D37">
         <v>0.999999970794792</v>
       </c>
-      <c r="E37" t="s">
-        <v>40</v>
+      <c r="E37">
+        <v>0.869283349749235</v>
       </c>
       <c r="F37">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>49.8062671416258</v>
+      </c>
+      <c r="G37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38">
-        <v>53.5282536663755</v>
+      <c r="B38" t="s">
+        <v>42</v>
       </c>
       <c r="C38">
-        <v>0.934244269320979</v>
+        <v>403</v>
       </c>
       <c r="D38">
         <v>1.00000002852137</v>
       </c>
-      <c r="E38" t="s">
-        <v>41</v>
+      <c r="E38">
+        <v>0.934244269320979</v>
       </c>
       <c r="F38">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>53.5282536663755</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39">
-        <v>47.0740609727696</v>
+      <c r="B39" t="s">
+        <v>43</v>
       </c>
       <c r="C39">
-        <v>0.821597356259394</v>
+        <v>404</v>
       </c>
       <c r="D39">
         <v>1.0000000136675</v>
       </c>
-      <c r="E39" t="s">
-        <v>42</v>
+      <c r="E39">
+        <v>0.821597356259394</v>
       </c>
       <c r="F39">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>47.0740609727696</v>
+      </c>
+      <c r="G39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40">
-        <v>39.7329405581425</v>
+      <c r="B40" t="s">
+        <v>44</v>
       </c>
       <c r="C40">
-        <v>0.69347063423878</v>
+        <v>405</v>
       </c>
       <c r="D40">
         <v>1.03396980691704</v>
       </c>
-      <c r="E40" t="s">
-        <v>43</v>
+      <c r="E40">
+        <v>0.69347063423878</v>
       </c>
       <c r="F40">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>39.7329405581425</v>
+      </c>
+      <c r="G40">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41">
-        <v>45.1428862956566</v>
+      <c r="B41" t="s">
+        <v>45</v>
       </c>
       <c r="C41">
-        <v>0.787891999712634</v>
+        <v>406</v>
       </c>
       <c r="D41">
         <v>1.03582701361177</v>
       </c>
-      <c r="E41" t="s">
-        <v>44</v>
+      <c r="E41">
+        <v>0.787891999712634</v>
       </c>
       <c r="F41">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>45.1428862956566</v>
+      </c>
+      <c r="G41">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42">
-        <v>47.4921282095683</v>
+      <c r="B42" t="s">
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>0.828894006036246</v>
+        <v>407</v>
       </c>
       <c r="D42">
         <v>1.04083757676905</v>
       </c>
-      <c r="E42" t="s">
-        <v>45</v>
+      <c r="E42">
+        <v>0.828894006036246</v>
       </c>
       <c r="F42">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>47.4921282095683</v>
+      </c>
+      <c r="G42">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43">
-        <v>42.2693097731927</v>
+      <c r="B43" t="s">
+        <v>47</v>
       </c>
       <c r="C43">
-        <v>0.737738628087631</v>
+        <v>408</v>
       </c>
       <c r="D43">
         <v>1.0368772557047</v>
       </c>
-      <c r="E43" t="s">
-        <v>46</v>
+      <c r="E43">
+        <v>0.737738628087631</v>
       </c>
       <c r="F43">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>42.2693097731927</v>
+      </c>
+      <c r="G43">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44">
-        <v>19.7786245271043</v>
+      <c r="B44" t="s">
+        <v>48</v>
       </c>
       <c r="C44">
-        <v>0.345202119513677</v>
+        <v>409</v>
       </c>
       <c r="D44">
         <v>1.00362084457578</v>
       </c>
-      <c r="E44" t="s">
-        <v>47</v>
+      <c r="E44">
+        <v>0.345202119513677</v>
       </c>
       <c r="F44">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>19.7786245271043</v>
+      </c>
+      <c r="G44">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45">
-        <v>14.6049383798835</v>
+      <c r="B45" t="s">
+        <v>49</v>
       </c>
       <c r="C45">
-        <v>0.254904261779854</v>
+        <v>410</v>
       </c>
       <c r="D45">
         <v>1.02869799081553</v>
       </c>
-      <c r="E45" t="s">
-        <v>48</v>
+      <c r="E45">
+        <v>0.254904261779854</v>
       </c>
       <c r="F45">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>14.6049383798835</v>
+      </c>
+      <c r="G45">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46">
-        <v>7.88668080450482</v>
+      <c r="B46" t="s">
+        <v>50</v>
       </c>
       <c r="C46">
-        <v>0.137648547092444</v>
+        <v>411</v>
       </c>
       <c r="D46">
         <v>0.997421262839202</v>
       </c>
-      <c r="E46" t="s">
-        <v>49</v>
+      <c r="E46">
+        <v>0.137648547092444</v>
       </c>
       <c r="F46">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>7.88668080450482</v>
+      </c>
+      <c r="G46">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47">
-        <v>6.9244039682491</v>
+      <c r="B47" t="s">
+        <v>51</v>
       </c>
       <c r="C47">
-        <v>0.120853647984108</v>
+        <v>412</v>
       </c>
       <c r="D47">
         <v>0.999999978205921</v>
       </c>
-      <c r="E47" t="s">
-        <v>50</v>
+      <c r="E47">
+        <v>0.120853647984108</v>
       </c>
       <c r="F47">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>6.9244039682491</v>
+      </c>
+      <c r="G47">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48">
-        <v>10.213706715535</v>
+      <c r="B48" t="s">
+        <v>52</v>
       </c>
       <c r="C48">
-        <v>0.178262811019141</v>
+        <v>413</v>
       </c>
       <c r="D48">
         <v>1.05246771802492</v>
       </c>
-      <c r="E48" t="s">
-        <v>51</v>
+      <c r="E48">
+        <v>0.178262811019141</v>
       </c>
       <c r="F48">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>10.213706715535</v>
+      </c>
+      <c r="G48">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49">
-        <v>9.75404854532221</v>
+      <c r="B49" t="s">
+        <v>53</v>
       </c>
       <c r="C49">
-        <v>0.170240262515236</v>
+        <v>414</v>
       </c>
       <c r="D49">
         <v>1.03941894733171</v>
       </c>
-      <c r="E49" t="s">
-        <v>52</v>
+      <c r="E49">
+        <v>0.170240262515236</v>
       </c>
       <c r="F49">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>9.75404854532221</v>
+      </c>
+      <c r="G49">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50">
-        <v>7.57432533230744</v>
+      <c r="B50" t="s">
+        <v>54</v>
       </c>
       <c r="C50">
-        <v>0.132196915665978</v>
+        <v>415</v>
       </c>
       <c r="D50">
         <v>1.04778619901921</v>
       </c>
-      <c r="E50" t="s">
-        <v>53</v>
+      <c r="E50">
+        <v>0.132196915665978</v>
       </c>
       <c r="F50">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>7.57432533230744</v>
+      </c>
+      <c r="G50">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51">
-        <v>3.67297449028735</v>
+      <c r="B51" t="s">
+        <v>55</v>
       </c>
       <c r="C51">
-        <v>0.0641054981972748</v>
+        <v>416</v>
       </c>
       <c r="D51">
         <v>1.0544469128387</v>
       </c>
-      <c r="E51" t="s">
-        <v>54</v>
+      <c r="E51">
+        <v>0.0641054981972748</v>
       </c>
       <c r="F51">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>3.67297449028735</v>
+      </c>
+      <c r="G51">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52">
-        <v>-33.4104910839929</v>
+      <c r="B52" t="s">
+        <v>56</v>
       </c>
       <c r="C52">
-        <v>-0.583123074123885</v>
+        <v>501</v>
       </c>
       <c r="D52">
         <v>1.00000002631667</v>
       </c>
-      <c r="E52" t="s">
-        <v>55</v>
+      <c r="E52">
+        <v>-0.583123074123885</v>
       </c>
       <c r="F52">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>-33.4104910839929</v>
+      </c>
+      <c r="G52">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53">
-        <v>-33.0177980825093</v>
+      <c r="B53" t="s">
+        <v>57</v>
       </c>
       <c r="C53">
-        <v>-0.576269288298457</v>
+        <v>502</v>
       </c>
       <c r="D53">
         <v>0.999999988943026</v>
       </c>
-      <c r="E53" t="s">
-        <v>56</v>
+      <c r="E53">
+        <v>-0.576269288298457</v>
       </c>
       <c r="F53">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>-33.0177980825093</v>
+      </c>
+      <c r="G53">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54">
-        <v>-37.2041765147009</v>
+      <c r="B54" t="s">
+        <v>58</v>
       </c>
       <c r="C54">
-        <v>-0.649335375674679</v>
+        <v>503</v>
       </c>
       <c r="D54">
         <v>0.999999996200133</v>
       </c>
-      <c r="E54" t="s">
-        <v>57</v>
+      <c r="E54">
+        <v>-0.649335375674679</v>
       </c>
       <c r="F54">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>-37.2041765147009</v>
+      </c>
+      <c r="G54">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55">
-        <v>-41.1682497543663</v>
+      <c r="B55" t="s">
+        <v>59</v>
       </c>
       <c r="C55">
-        <v>-0.718521505497039</v>
+        <v>504</v>
       </c>
       <c r="D55">
         <v>1.04223782000947</v>
       </c>
-      <c r="E55" t="s">
-        <v>58</v>
+      <c r="E55">
+        <v>-0.718521505497039</v>
       </c>
       <c r="F55">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>-41.1682497543663</v>
+      </c>
+      <c r="G55">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56">
-        <v>-39.8830064017147</v>
+      <c r="B56" t="s">
+        <v>60</v>
       </c>
       <c r="C56">
-        <v>-0.696089777303898</v>
+        <v>505</v>
       </c>
       <c r="D56">
         <v>1.01219769911013</v>
       </c>
-      <c r="E56" t="s">
-        <v>59</v>
+      <c r="E56">
+        <v>-0.696089777303898</v>
       </c>
       <c r="F56">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>-39.8830064017147</v>
+      </c>
+      <c r="G56">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57">
-        <v>-42.0474942555633</v>
+      <c r="B57" t="s">
+        <v>61</v>
       </c>
       <c r="C57">
-        <v>-0.733867216972982</v>
+        <v>506</v>
       </c>
       <c r="D57">
         <v>1.01517424612786</v>
       </c>
-      <c r="E57" t="s">
-        <v>60</v>
+      <c r="E57">
+        <v>-0.733867216972982</v>
       </c>
       <c r="F57">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>-42.0474942555633</v>
+      </c>
+      <c r="G57">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58">
-        <v>-42.5625663828966</v>
+      <c r="B58" t="s">
+        <v>62</v>
       </c>
       <c r="C58">
-        <v>-0.742856921480199</v>
+        <v>507</v>
       </c>
       <c r="D58">
         <v>1.01500002191357</v>
       </c>
-      <c r="E58" t="s">
-        <v>61</v>
+      <c r="E58">
+        <v>-0.742856921480199</v>
       </c>
       <c r="F58">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>-42.5625663828966</v>
+      </c>
+      <c r="G58">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59">
-        <v>-43.0584272684546</v>
+      <c r="B59" t="s">
+        <v>63</v>
       </c>
       <c r="C59">
-        <v>-0.751511326565041</v>
+        <v>508</v>
       </c>
       <c r="D59">
         <v>1.01055972211508</v>
       </c>
-      <c r="E59" t="s">
-        <v>62</v>
+      <c r="E59">
+        <v>-0.751511326565041</v>
       </c>
       <c r="F59">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>-43.0584272684546</v>
+      </c>
+      <c r="G59">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60">
-        <v>-36.7436696816194</v>
+      <c r="B60" t="s">
+        <v>64</v>
       </c>
       <c r="C60">
-        <v>-0.641298015209475</v>
+        <v>509</v>
       </c>
       <c r="D60">
         <v>1.03000001529242</v>
       </c>
-      <c r="E60" t="s">
-        <v>63</v>
+      <c r="E60">
+        <v>-0.641298015209475</v>
       </c>
       <c r="F60">
-        <v>509</v>
+        <v>-36.7436696816194</v>
+      </c>
+      <c r="G60">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -2000,1474 +2198,3049 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>66</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2">
         <v>-178.195266723633</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>-9.12441635131836</v>
       </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>180.887842178345</v>
+      </c>
+      <c r="F2">
+        <v>30.5047473907471</v>
+      </c>
+      <c r="G2">
+        <v>102</v>
+      </c>
+      <c r="H2">
+        <v>217</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3">
         <v>-178.195266723633</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-9.12441635131836</v>
       </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>180.887842178345</v>
+      </c>
+      <c r="F3">
+        <v>30.5047473907471</v>
+      </c>
+      <c r="G3">
+        <v>102</v>
+      </c>
+      <c r="H3">
+        <v>217</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4">
         <v>-191.711227416992</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>-3.75087857246399</v>
       </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>194.605007648468</v>
+      </c>
+      <c r="F4">
+        <v>26.7527210712433</v>
+      </c>
+      <c r="G4">
+        <v>102</v>
+      </c>
+      <c r="H4">
+        <v>217</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
         <v>-191.711227416992</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-3.75087857246399</v>
       </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>194.605007648468</v>
+      </c>
+      <c r="F5">
+        <v>26.7527210712433</v>
+      </c>
+      <c r="G5">
+        <v>102</v>
+      </c>
+      <c r="H5">
+        <v>217</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
         <v>-83.0616760253906</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>-42.0610313415527</v>
       </c>
-      <c r="D6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>83.3819034993649</v>
+      </c>
+      <c r="F6">
+        <v>44.5943865776062</v>
+      </c>
+      <c r="G6">
+        <v>102</v>
+      </c>
+      <c r="H6">
+        <v>309</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7">
         <v>-83.0616760253906</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-42.0610313415527</v>
       </c>
-      <c r="D7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>83.3819034993649</v>
+      </c>
+      <c r="F7">
+        <v>44.5943865776062</v>
+      </c>
+      <c r="G7">
+        <v>102</v>
+      </c>
+      <c r="H7">
+        <v>309</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8">
         <v>-34.0636749267578</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-47.0143089294434</v>
       </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>34.1941784769297</v>
+      </c>
+      <c r="F8">
+        <v>48.0535482168198</v>
+      </c>
+      <c r="G8">
+        <v>102</v>
+      </c>
+      <c r="H8">
+        <v>309</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9">
         <v>14.8352127075195</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-31.0145492553711</v>
       </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>-14.7813339792192</v>
+      </c>
+      <c r="F9">
+        <v>31.4410891830921</v>
+      </c>
+      <c r="G9">
+        <v>205</v>
+      </c>
+      <c r="H9">
+        <v>206</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10">
         <v>14.8352127075195</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-31.0145492553711</v>
       </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-14.7813339792192</v>
+      </c>
+      <c r="F10">
+        <v>31.4410891830921</v>
+      </c>
+      <c r="G10">
+        <v>205</v>
+      </c>
+      <c r="H10">
+        <v>206</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11">
         <v>-159.835220336914</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-43.1428260803223</v>
       </c>
-      <c r="D11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>160.701179504395</v>
+      </c>
+      <c r="F11">
+        <v>53.908805847168</v>
+      </c>
+      <c r="G11">
+        <v>205</v>
+      </c>
+      <c r="H11">
+        <v>416</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12">
         <v>-159.835220336914</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-43.1428260803223</v>
       </c>
-      <c r="D12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>160.701179504395</v>
+      </c>
+      <c r="F12">
+        <v>53.908805847168</v>
+      </c>
+      <c r="G12">
+        <v>205</v>
+      </c>
+      <c r="H12">
+        <v>416</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13">
         <v>554.190063476562</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>18.0564498901367</v>
       </c>
-      <c r="D13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>-541.071931838989</v>
+      </c>
+      <c r="F13">
+        <v>85.722541809082</v>
+      </c>
+      <c r="G13">
+        <v>206</v>
+      </c>
+      <c r="H13">
+        <v>207</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14">
         <v>554.190063476562</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>18.0564498901367</v>
       </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>-541.071931838989</v>
+      </c>
+      <c r="F14">
+        <v>85.722541809082</v>
+      </c>
+      <c r="G14">
+        <v>206</v>
+      </c>
+      <c r="H14">
+        <v>207</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15">
         <v>590.595275878906</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>4.78864002227783</v>
       </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>-568.769876480103</v>
+      </c>
+      <c r="F15">
+        <v>169.483866691589</v>
+      </c>
+      <c r="G15">
+        <v>206</v>
+      </c>
+      <c r="H15">
+        <v>212</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16">
         <v>590.595275878906</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>4.78864002227783</v>
       </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>-568.769876480103</v>
+      </c>
+      <c r="F16">
+        <v>169.483866691589</v>
+      </c>
+      <c r="G16">
+        <v>206</v>
+      </c>
+      <c r="H16">
+        <v>212</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17">
         <v>219.995971679688</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-40.6313591003418</v>
       </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>-216.978173017502</v>
+      </c>
+      <c r="F17">
+        <v>64.7280235290527</v>
+      </c>
+      <c r="G17">
+        <v>206</v>
+      </c>
+      <c r="H17">
+        <v>215</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18">
         <v>219.995971679688</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-40.6313591003418</v>
       </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>-216.978173017502</v>
+      </c>
+      <c r="F18">
+        <v>64.7280235290527</v>
+      </c>
+      <c r="G18">
+        <v>206</v>
+      </c>
+      <c r="H18">
+        <v>215</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19">
         <v>178.441986083984</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-70.5516815185547</v>
       </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>-177.811147212982</v>
+      </c>
+      <c r="F19">
+        <v>75.4582061767578</v>
+      </c>
+      <c r="G19">
+        <v>207</v>
+      </c>
+      <c r="H19">
+        <v>208</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20">
         <v>178.441986083984</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-70.5516815185547</v>
       </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>-177.811147212982</v>
+      </c>
+      <c r="F20">
+        <v>75.4582061767578</v>
+      </c>
+      <c r="G20">
+        <v>207</v>
+      </c>
+      <c r="H20">
+        <v>208</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21">
         <v>-684.740173339844</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>-84.5732421875</v>
       </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>688.477082490921</v>
+      </c>
+      <c r="F21">
+        <v>113.534290313721</v>
+      </c>
+      <c r="G21">
+        <v>207</v>
+      </c>
+      <c r="H21">
+        <v>209</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22">
         <v>371.874084472656</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-31.9466361999512</v>
       </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>-367.70109128952</v>
+      </c>
+      <c r="F22">
+        <v>65.3305816650391</v>
+      </c>
+      <c r="G22">
+        <v>208</v>
+      </c>
+      <c r="H22">
+        <v>211</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23">
         <v>371.874084472656</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>-31.9466361999512</v>
       </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23">
+        <v>-367.70109128952</v>
+      </c>
+      <c r="F23">
+        <v>65.3305816650391</v>
+      </c>
+      <c r="G23">
+        <v>208</v>
+      </c>
+      <c r="H23">
+        <v>211</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24">
         <v>371.874084472656</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-31.9466361999512</v>
       </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24">
+        <v>-367.70109128952</v>
+      </c>
+      <c r="F24">
+        <v>65.3305816650391</v>
+      </c>
+      <c r="G24">
+        <v>208</v>
+      </c>
+      <c r="H24">
+        <v>211</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25">
         <v>435.835754394531</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>-35.0941390991211</v>
       </c>
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25">
+        <v>-427.61391544342</v>
+      </c>
+      <c r="F25">
+        <v>100.138023376465</v>
+      </c>
+      <c r="G25">
+        <v>209</v>
+      </c>
+      <c r="H25">
+        <v>212</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26">
         <v>397.843627929688</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>-48.2113990783691</v>
       </c>
-      <c r="D26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26">
+        <v>-396.397180080414</v>
+      </c>
+      <c r="F26">
+        <v>69.1848907470703</v>
+      </c>
+      <c r="G26">
+        <v>210</v>
+      </c>
+      <c r="H26">
+        <v>213</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27">
         <v>397.843627929688</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>-48.2113990783691</v>
       </c>
-      <c r="D27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27">
+        <v>-396.397180080414</v>
+      </c>
+      <c r="F27">
+        <v>69.1848907470703</v>
+      </c>
+      <c r="G27">
+        <v>210</v>
+      </c>
+      <c r="H27">
+        <v>213</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28">
         <v>-61.7906265258789</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-48.7641944885254</v>
       </c>
-      <c r="D28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28">
+        <v>61.8669961318374</v>
+      </c>
+      <c r="F28">
+        <v>49.3533315062523</v>
+      </c>
+      <c r="G28">
+        <v>211</v>
+      </c>
+      <c r="H28">
+        <v>212</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29">
         <v>-61.7906265258789</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-48.7641944885254</v>
       </c>
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29">
+        <v>61.8669961318374</v>
+      </c>
+      <c r="F29">
+        <v>49.3533315062523</v>
+      </c>
+      <c r="G29">
+        <v>211</v>
+      </c>
+      <c r="H29">
+        <v>212</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30">
         <v>-48.3154525756836</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>-134.890914916992</v>
       </c>
-      <c r="D30" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30">
+        <v>48.6499094367027</v>
+      </c>
+      <c r="F30">
+        <v>137.619378805161</v>
+      </c>
+      <c r="G30">
+        <v>211</v>
+      </c>
+      <c r="H30">
+        <v>214</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31">
         <v>196.419769287109</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-41.5021362304688</v>
       </c>
-      <c r="D31" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31">
+        <v>-193.804323673248</v>
+      </c>
+      <c r="F31">
+        <v>62.3509731292725</v>
+      </c>
+      <c r="G31">
+        <v>212</v>
+      </c>
+      <c r="H31">
+        <v>217</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32">
         <v>455.451049804688</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>35.4196739196777</v>
       </c>
-      <c r="D32" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32">
+        <v>-453.485705256462</v>
+      </c>
+      <c r="F32">
+        <v>-20.2865228652954</v>
+      </c>
+      <c r="G32">
+        <v>214</v>
+      </c>
+      <c r="H32">
+        <v>216</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33">
         <v>288.693389892578</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>4.16860008239746</v>
       </c>
-      <c r="D33" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33">
+        <v>-284.814564704895</v>
+      </c>
+      <c r="F33">
+        <v>26.5453624725342</v>
+      </c>
+      <c r="G33">
+        <v>214</v>
+      </c>
+      <c r="H33">
+        <v>217</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34">
         <v>574.383178710938</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>-33.8456649780273</v>
       </c>
-      <c r="D34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34">
+        <v>-558.355630874634</v>
+      </c>
+      <c r="F34">
+        <v>160.49471282959</v>
+      </c>
+      <c r="G34">
+        <v>215</v>
+      </c>
+      <c r="H34">
+        <v>216</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35">
         <v>574.383178710938</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>-33.8456649780273</v>
       </c>
-      <c r="D35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35">
+        <v>-558.355630874634</v>
+      </c>
+      <c r="F35">
+        <v>160.49471282959</v>
+      </c>
+      <c r="G35">
+        <v>215</v>
+      </c>
+      <c r="H35">
+        <v>216</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36">
         <v>531.412414550781</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-2.86908435821533</v>
       </c>
-      <c r="D36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36">
+        <v>-511.968439102173</v>
+      </c>
+      <c r="F36">
+        <v>157.880787849426</v>
+      </c>
+      <c r="G36">
+        <v>215</v>
+      </c>
+      <c r="H36">
+        <v>217</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37">
         <v>531.412414550781</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>-2.86908435821533</v>
       </c>
-      <c r="D37" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37">
+        <v>-511.968439102173</v>
+      </c>
+      <c r="F37">
+        <v>157.880787849426</v>
+      </c>
+      <c r="G37">
+        <v>215</v>
+      </c>
+      <c r="H37">
+        <v>217</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38">
         <v>190.196914672852</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>-12.0481414794922</v>
       </c>
-      <c r="D38" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38">
+        <v>-188.42989718914</v>
+      </c>
+      <c r="F38">
+        <v>26.011043548584</v>
+      </c>
+      <c r="G38">
+        <v>216</v>
+      </c>
+      <c r="H38">
+        <v>217</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39">
         <v>735.888244628906</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>48.9376068115234</v>
       </c>
-      <c r="D39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39">
+        <v>-725.48452091217</v>
+      </c>
+      <c r="F39">
+        <v>96.7145233154297</v>
+      </c>
+      <c r="G39">
+        <v>303</v>
+      </c>
+      <c r="H39">
+        <v>304</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40">
         <v>735.888244628906</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>48.9376068115234</v>
       </c>
-      <c r="D40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40">
+        <v>-725.48452091217</v>
+      </c>
+      <c r="F40">
+        <v>96.7145233154297</v>
+      </c>
+      <c r="G40">
+        <v>303</v>
+      </c>
+      <c r="H40">
+        <v>304</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41">
         <v>1464.11181640625</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>28.0773391723633</v>
       </c>
-      <c r="D41" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41">
+        <v>-1441.63615226746</v>
+      </c>
+      <c r="F41">
+        <v>298.841484069824</v>
+      </c>
+      <c r="G41">
+        <v>303</v>
+      </c>
+      <c r="H41">
+        <v>305</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42">
         <v>1464.11181640625</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>28.0773391723633</v>
       </c>
-      <c r="D42" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42">
+        <v>-1441.63615226746</v>
+      </c>
+      <c r="F42">
+        <v>298.841484069824</v>
+      </c>
+      <c r="G42">
+        <v>303</v>
+      </c>
+      <c r="H42">
+        <v>305</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43">
         <v>646.835327148438</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-314.718566894531</v>
       </c>
-      <c r="D43" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43">
+        <v>-645.349394798279</v>
+      </c>
+      <c r="F43">
+        <v>334.53099822998</v>
+      </c>
+      <c r="G43">
+        <v>304</v>
+      </c>
+      <c r="H43">
+        <v>305</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44">
         <v>1075.01306152344</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-120.928153991699</v>
       </c>
-      <c r="D44" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44">
+        <v>-1072.76661944389</v>
+      </c>
+      <c r="F44">
+        <v>154.624782562256</v>
+      </c>
+      <c r="G44">
+        <v>305</v>
+      </c>
+      <c r="H44">
+        <v>306</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45">
         <v>716.279663085938</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>-152.756729125977</v>
       </c>
-      <c r="D45" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45">
+        <v>-714.749165773392</v>
+      </c>
+      <c r="F45">
+        <v>175.71418762207</v>
+      </c>
+      <c r="G45">
+        <v>305</v>
+      </c>
+      <c r="H45">
+        <v>307</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46">
         <v>716.279663085938</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>-152.756729125977</v>
       </c>
-      <c r="D46" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46">
+        <v>-714.749165773392</v>
+      </c>
+      <c r="F46">
+        <v>175.71418762207</v>
+      </c>
+      <c r="G46">
+        <v>305</v>
+      </c>
+      <c r="H46">
+        <v>307</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47">
         <v>-12.2334794998169</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>-231.343246459961</v>
       </c>
-      <c r="D47" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47">
+        <v>12.2821125201881</v>
+      </c>
+      <c r="F47">
+        <v>231.926842749119</v>
+      </c>
+      <c r="G47">
+        <v>306</v>
+      </c>
+      <c r="H47">
+        <v>307</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48">
         <v>418.608093261719</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-268.435241699219</v>
       </c>
-      <c r="D48" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48">
+        <v>-414.588022232056</v>
+      </c>
+      <c r="F48">
+        <v>325.240589141846</v>
+      </c>
+      <c r="G48">
+        <v>307</v>
+      </c>
+      <c r="H48">
+        <v>308</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
         <v>418.608093261719</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>-268.435241699219</v>
       </c>
-      <c r="D49" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49">
+        <v>-414.588022232056</v>
+      </c>
+      <c r="F49">
+        <v>325.240589141846</v>
+      </c>
+      <c r="G49">
+        <v>307</v>
+      </c>
+      <c r="H49">
+        <v>308</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
         <v>-123.65266418457</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>3.96901965141296</v>
       </c>
-      <c r="D50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50">
+        <v>125.778451681137</v>
+      </c>
+      <c r="F50">
+        <v>12.8719398975372</v>
+      </c>
+      <c r="G50">
+        <v>309</v>
+      </c>
+      <c r="H50">
+        <v>310</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51">
         <v>-123.65266418457</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>3.96901965141296</v>
       </c>
-      <c r="D51" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51">
+        <v>125.778451681137</v>
+      </c>
+      <c r="F51">
+        <v>12.8719398975372</v>
+      </c>
+      <c r="G51">
+        <v>309</v>
+      </c>
+      <c r="H51">
+        <v>310</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52">
         <v>-123.65266418457</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>3.96901965141296</v>
       </c>
-      <c r="D52" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52">
+        <v>125.778451681137</v>
+      </c>
+      <c r="F52">
+        <v>12.8719398975372</v>
+      </c>
+      <c r="G52">
+        <v>309</v>
+      </c>
+      <c r="H52">
+        <v>310</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53">
         <v>-188.667678833008</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>71.185173034668</v>
       </c>
-      <c r="D53" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53">
+        <v>188.667678833008</v>
+      </c>
+      <c r="F53">
+        <v>-84.5624361038208</v>
+      </c>
+      <c r="G53">
+        <v>310</v>
+      </c>
+      <c r="H53">
+        <v>311</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54">
         <v>-188.667678833008</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>71.185173034668</v>
       </c>
-      <c r="D54" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54">
+        <v>188.667678833008</v>
+      </c>
+      <c r="F54">
+        <v>-84.5624361038208</v>
+      </c>
+      <c r="G54">
+        <v>310</v>
+      </c>
+      <c r="H54">
+        <v>311</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55">
         <v>307.000030517578</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>1.65619707107544</v>
       </c>
-      <c r="D55" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55">
+        <v>-301.670835018158</v>
+      </c>
+      <c r="F55">
+        <v>38.3127703666687</v>
+      </c>
+      <c r="G55">
+        <v>312</v>
+      </c>
+      <c r="H55">
+        <v>313</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56">
         <v>307.000030517578</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>1.65619707107544</v>
       </c>
-      <c r="D56" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56">
+        <v>-301.670835018158</v>
+      </c>
+      <c r="F56">
+        <v>38.3127703666687</v>
+      </c>
+      <c r="G56">
+        <v>312</v>
+      </c>
+      <c r="H56">
+        <v>313</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="s">
+        <v>101</v>
+      </c>
+      <c r="C57">
         <v>307.000030517578</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>1.65619707107544</v>
       </c>
-      <c r="D57" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57">
+        <v>-301.670835018158</v>
+      </c>
+      <c r="F57">
+        <v>38.3127703666687</v>
+      </c>
+      <c r="G57">
+        <v>312</v>
+      </c>
+      <c r="H57">
+        <v>313</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58">
         <v>-210.426849365234</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>-7.96283769607544</v>
       </c>
-      <c r="D58" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58">
+        <v>210.85693949461</v>
+      </c>
+      <c r="F58">
+        <v>12.2637386322021</v>
+      </c>
+      <c r="G58">
+        <v>313</v>
+      </c>
+      <c r="H58">
+        <v>314</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59">
         <v>-210.426849365234</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>-7.96283769607544</v>
       </c>
-      <c r="D59" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59">
+        <v>210.85693949461</v>
+      </c>
+      <c r="F59">
+        <v>12.2637386322021</v>
+      </c>
+      <c r="G59">
+        <v>313</v>
+      </c>
+      <c r="H59">
+        <v>314</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60">
         <v>124.587997436523</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>11.3256254196167</v>
       </c>
-      <c r="D60" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60">
+        <v>-123.56676864624</v>
+      </c>
+      <c r="F60">
+        <v>-4.03113460540771</v>
+      </c>
+      <c r="G60">
+        <v>315</v>
+      </c>
+      <c r="H60">
+        <v>509</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61">
         <v>124.587997436523</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>11.3256254196167</v>
       </c>
-      <c r="D61" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61">
+        <v>-123.56676864624</v>
+      </c>
+      <c r="F61">
+        <v>-4.03113460540771</v>
+      </c>
+      <c r="G61">
+        <v>315</v>
+      </c>
+      <c r="H61">
+        <v>509</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>60</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62">
         <v>-210.6689453125</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>2.9316201210022</v>
       </c>
-      <c r="D62" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62">
+        <v>212.307757139206</v>
+      </c>
+      <c r="F62">
+        <v>17.0282683372498</v>
+      </c>
+      <c r="G62">
+        <v>405</v>
+      </c>
+      <c r="H62">
+        <v>406</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63">
         <v>-210.6689453125</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>2.9316201210022</v>
       </c>
-      <c r="D63" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63">
+        <v>212.307757139206</v>
+      </c>
+      <c r="F63">
+        <v>17.0282683372498</v>
+      </c>
+      <c r="G63">
+        <v>405</v>
+      </c>
+      <c r="H63">
+        <v>406</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64">
         <v>-94.2118606567383</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>-3.83989000320435</v>
       </c>
-      <c r="D64" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64">
+        <v>94.6621630787849</v>
+      </c>
+      <c r="F64">
+        <v>8.00935649871826</v>
+      </c>
+      <c r="G64">
+        <v>405</v>
+      </c>
+      <c r="H64">
+        <v>408</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65">
         <v>295.183288574219</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>-8.9947338104248</v>
       </c>
-      <c r="D65" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65">
+        <v>-280.326979637146</v>
+      </c>
+      <c r="F65">
+        <v>109.687498092651</v>
+      </c>
+      <c r="G65">
+        <v>405</v>
+      </c>
+      <c r="H65">
+        <v>409</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>64</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66">
         <v>295.183288574219</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>-8.9947338104248</v>
       </c>
-      <c r="D66" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66">
+        <v>-280.326979637146</v>
+      </c>
+      <c r="F66">
+        <v>109.687498092651</v>
+      </c>
+      <c r="G66">
+        <v>405</v>
+      </c>
+      <c r="H66">
+        <v>409</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67">
         <v>295.183288574219</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-8.9947338104248</v>
       </c>
-      <c r="D67" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="E67">
+        <v>-280.326979637146</v>
+      </c>
+      <c r="F67">
+        <v>109.687498092651</v>
+      </c>
+      <c r="G67">
+        <v>405</v>
+      </c>
+      <c r="H67">
+        <v>409</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>66</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68">
         <v>-582.307739257812</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>-13.7225780487061</v>
       </c>
-      <c r="D68" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="E68">
+        <v>584.204534173012</v>
+      </c>
+      <c r="F68">
+        <v>37.7486457824707</v>
+      </c>
+      <c r="G68">
+        <v>406</v>
+      </c>
+      <c r="H68">
+        <v>407</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>67</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="s">
+        <v>107</v>
+      </c>
+      <c r="C69">
         <v>-582.307739257812</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>-13.7225780487061</v>
       </c>
-      <c r="D69" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69">
+        <v>584.204534173012</v>
+      </c>
+      <c r="F69">
+        <v>37.7486457824707</v>
+      </c>
+      <c r="G69">
+        <v>406</v>
+      </c>
+      <c r="H69">
+        <v>407</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>68</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70">
         <v>191.590942382812</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>-21.2331123352051</v>
       </c>
-      <c r="D70" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70">
+        <v>-190.167803883553</v>
+      </c>
+      <c r="F70">
+        <v>38.6157341003418</v>
+      </c>
+      <c r="G70">
+        <v>407</v>
+      </c>
+      <c r="H70">
+        <v>408</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>69</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71">
         <v>261.835205078125</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>9.22804737091064</v>
       </c>
-      <c r="D71" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71">
+        <v>-250.996862411499</v>
+      </c>
+      <c r="F71">
+        <v>116.890849113464</v>
+      </c>
+      <c r="G71">
+        <v>408</v>
+      </c>
+      <c r="H71">
+        <v>410</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>70</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="s">
+        <v>109</v>
+      </c>
+      <c r="C72">
         <v>261.835205078125</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>9.22804737091064</v>
       </c>
-      <c r="D72" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="E72">
+        <v>-250.996862411499</v>
+      </c>
+      <c r="F72">
+        <v>116.890849113464</v>
+      </c>
+      <c r="G72">
+        <v>408</v>
+      </c>
+      <c r="H72">
+        <v>410</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>71</v>
       </c>
-      <c r="B73">
+      <c r="B73" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73">
         <v>261.835205078125</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>9.22804737091064</v>
       </c>
-      <c r="D73" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="E73">
+        <v>-250.996862411499</v>
+      </c>
+      <c r="F73">
+        <v>116.890849113464</v>
+      </c>
+      <c r="G73">
+        <v>408</v>
+      </c>
+      <c r="H73">
+        <v>410</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>72</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74">
         <v>290.490447998047</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>-26.2899627685547</v>
       </c>
-      <c r="D74" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="E74">
+        <v>-281.860427856445</v>
+      </c>
+      <c r="F74">
+        <v>85.6946640014648</v>
+      </c>
+      <c r="G74">
+        <v>409</v>
+      </c>
+      <c r="H74">
+        <v>411</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>73</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75">
         <v>290.490447998047</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>-26.2899627685547</v>
       </c>
-      <c r="D75" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="E75">
+        <v>-281.860427856445</v>
+      </c>
+      <c r="F75">
+        <v>85.6946640014648</v>
+      </c>
+      <c r="G75">
+        <v>409</v>
+      </c>
+      <c r="H75">
+        <v>411</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>74</v>
       </c>
-      <c r="B76">
+      <c r="B76" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76">
         <v>230.083709716797</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>32.5313758850098</v>
       </c>
-      <c r="D76" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="E76">
+        <v>-227.80911564827</v>
+      </c>
+      <c r="F76">
+        <v>-4.3898868560791</v>
+      </c>
+      <c r="G76">
+        <v>410</v>
+      </c>
+      <c r="H76">
+        <v>411</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>75</v>
       </c>
-      <c r="B77">
+      <c r="B77" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77">
         <v>262.602233886719</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>29.0207023620605</v>
       </c>
-      <c r="D77" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="E77">
+        <v>-259.69184756279</v>
+      </c>
+      <c r="F77">
+        <v>6.98686599731445</v>
+      </c>
+      <c r="G77">
+        <v>410</v>
+      </c>
+      <c r="H77">
+        <v>412</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>76</v>
       </c>
-      <c r="B78">
+      <c r="B78" t="s">
+        <v>112</v>
+      </c>
+      <c r="C78">
         <v>262.602233886719</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>29.0207023620605</v>
       </c>
-      <c r="D78" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78">
+        <v>-259.69184756279</v>
+      </c>
+      <c r="F78">
+        <v>6.98686599731445</v>
+      </c>
+      <c r="G78">
+        <v>410</v>
+      </c>
+      <c r="H78">
+        <v>412</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>77</v>
       </c>
-      <c r="B79">
+      <c r="B79" t="s">
+        <v>112</v>
+      </c>
+      <c r="C79">
         <v>262.602233886719</v>
       </c>
-      <c r="C79">
+      <c r="D79">
         <v>29.0207023620605</v>
       </c>
-      <c r="D79" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="E79">
+        <v>-259.69184756279</v>
+      </c>
+      <c r="F79">
+        <v>6.98686599731445</v>
+      </c>
+      <c r="G79">
+        <v>410</v>
+      </c>
+      <c r="H79">
+        <v>412</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>78</v>
       </c>
-      <c r="B80">
+      <c r="B80" t="s">
+        <v>112</v>
+      </c>
+      <c r="C80">
         <v>262.602233886719</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>29.0207023620605</v>
       </c>
-      <c r="D80" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80">
+        <v>-259.69184756279</v>
+      </c>
+      <c r="F80">
+        <v>6.98686599731445</v>
+      </c>
+      <c r="G80">
+        <v>410</v>
+      </c>
+      <c r="H80">
+        <v>412</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>79</v>
       </c>
-      <c r="B81">
+      <c r="B81" t="s">
+        <v>113</v>
+      </c>
+      <c r="C81">
         <v>163.248977661133</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>-77.4470748901367</v>
       </c>
-      <c r="D81" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81">
+        <v>-162.121877908707</v>
+      </c>
+      <c r="F81">
+        <v>91.366756439209</v>
+      </c>
+      <c r="G81">
+        <v>410</v>
+      </c>
+      <c r="H81">
+        <v>413</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>80</v>
       </c>
-      <c r="B82">
+      <c r="B82" t="s">
+        <v>113</v>
+      </c>
+      <c r="C82">
         <v>163.248977661133</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>-77.4470748901367</v>
       </c>
-      <c r="D82" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="E82">
+        <v>-162.121877908707</v>
+      </c>
+      <c r="F82">
+        <v>91.366756439209</v>
+      </c>
+      <c r="G82">
+        <v>410</v>
+      </c>
+      <c r="H82">
+        <v>413</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>81</v>
       </c>
-      <c r="B83">
+      <c r="B83" t="s">
+        <v>114</v>
+      </c>
+      <c r="C83">
         <v>108.264984130859</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>-30.6120872497559</v>
       </c>
-      <c r="D83" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+      <c r="E83">
+        <v>-108.116334155202</v>
+      </c>
+      <c r="F83">
+        <v>32.4949867725372</v>
+      </c>
+      <c r="G83">
+        <v>411</v>
+      </c>
+      <c r="H83">
+        <v>412</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
         <v>82</v>
       </c>
-      <c r="B84">
+      <c r="B84" t="s">
+        <v>114</v>
+      </c>
+      <c r="C84">
         <v>108.264984130859</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>-30.6120872497559</v>
       </c>
-      <c r="D84" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+      <c r="E84">
+        <v>-108.116334155202</v>
+      </c>
+      <c r="F84">
+        <v>32.4949867725372</v>
+      </c>
+      <c r="G84">
+        <v>411</v>
+      </c>
+      <c r="H84">
+        <v>412</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>83</v>
       </c>
-      <c r="B85">
+      <c r="B85" t="s">
+        <v>115</v>
+      </c>
+      <c r="C85">
         <v>162.121887207031</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>-65.6737060546875</v>
       </c>
-      <c r="D85" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="E85">
+        <v>-161.598499119282</v>
+      </c>
+      <c r="F85">
+        <v>72.2160573005676</v>
+      </c>
+      <c r="G85">
+        <v>414</v>
+      </c>
+      <c r="H85">
+        <v>415</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>84</v>
       </c>
-      <c r="B86">
+      <c r="B86" t="s">
+        <v>115</v>
+      </c>
+      <c r="C86">
         <v>162.121887207031</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>-65.6737060546875</v>
       </c>
-      <c r="D86" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="E86">
+        <v>-161.598499119282</v>
+      </c>
+      <c r="F86">
+        <v>72.2160573005676</v>
+      </c>
+      <c r="G86">
+        <v>414</v>
+      </c>
+      <c r="H86">
+        <v>415</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>85</v>
       </c>
-      <c r="B87">
+      <c r="B87" t="s">
+        <v>116</v>
+      </c>
+      <c r="C87">
         <v>161.598495483398</v>
       </c>
-      <c r="C87">
+      <c r="D87">
         <v>-62.675910949707</v>
       </c>
-      <c r="D87" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="E87">
+        <v>-160.701177656651</v>
+      </c>
+      <c r="F87">
+        <v>73.8317556381226</v>
+      </c>
+      <c r="G87">
+        <v>415</v>
+      </c>
+      <c r="H87">
+        <v>416</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>86</v>
       </c>
-      <c r="B88">
+      <c r="B88" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88">
         <v>161.598495483398</v>
       </c>
-      <c r="C88">
+      <c r="D88">
         <v>-62.675910949707</v>
       </c>
-      <c r="D88" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+      <c r="E88">
+        <v>-160.701177656651</v>
+      </c>
+      <c r="F88">
+        <v>73.8317556381226</v>
+      </c>
+      <c r="G88">
+        <v>415</v>
+      </c>
+      <c r="H88">
+        <v>416</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" s="1">
         <v>87</v>
       </c>
-      <c r="B89">
+      <c r="B89" t="s">
+        <v>117</v>
+      </c>
+      <c r="C89">
         <v>19.6331329345703</v>
       </c>
-      <c r="C89">
+      <c r="D89">
         <v>-14.291332244873</v>
       </c>
-      <c r="D89" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+      <c r="E89">
+        <v>-19.496469900012</v>
+      </c>
+      <c r="F89">
+        <v>15.1826128959656</v>
+      </c>
+      <c r="G89">
+        <v>504</v>
+      </c>
+      <c r="H89">
+        <v>507</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="1">
         <v>88</v>
       </c>
-      <c r="B90">
+      <c r="B90" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90">
         <v>19.6331329345703</v>
       </c>
-      <c r="C90">
+      <c r="D90">
         <v>-14.291332244873</v>
       </c>
-      <c r="D90" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="E90">
+        <v>-19.496469900012</v>
+      </c>
+      <c r="F90">
+        <v>15.1826128959656</v>
+      </c>
+      <c r="G90">
+        <v>504</v>
+      </c>
+      <c r="H90">
+        <v>507</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" s="1">
         <v>89</v>
       </c>
-      <c r="B91">
+      <c r="B91" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91">
         <v>147.86686706543</v>
       </c>
-      <c r="C91">
+      <c r="D91">
         <v>-72.8111190795898</v>
       </c>
-      <c r="D91" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+      <c r="E91">
+        <v>-142.477138996124</v>
+      </c>
+      <c r="F91">
+        <v>76.7497663497925</v>
+      </c>
+      <c r="G91">
+        <v>504</v>
+      </c>
+      <c r="H91">
+        <v>508</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" s="1">
         <v>90</v>
       </c>
-      <c r="B92">
+      <c r="B92" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92">
         <v>147.86686706543</v>
       </c>
-      <c r="C92">
+      <c r="D92">
         <v>-72.8111190795898</v>
       </c>
-      <c r="D92" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+      <c r="E92">
+        <v>-142.477138996124</v>
+      </c>
+      <c r="F92">
+        <v>76.7497663497925</v>
+      </c>
+      <c r="G92">
+        <v>504</v>
+      </c>
+      <c r="H92">
+        <v>508</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" s="1">
         <v>91</v>
       </c>
-      <c r="B93">
+      <c r="B93" t="s">
+        <v>119</v>
+      </c>
+      <c r="C93">
         <v>279.109375</v>
       </c>
-      <c r="C93">
+      <c r="D93">
         <v>-37.8834114074707</v>
       </c>
-      <c r="D93" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+      <c r="E93">
+        <v>-277.872171163559</v>
+      </c>
+      <c r="F93">
+        <v>51.0287036895752</v>
+      </c>
+      <c r="G93">
+        <v>505</v>
+      </c>
+      <c r="H93">
+        <v>507</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" s="1">
         <v>92</v>
       </c>
-      <c r="B94">
+      <c r="B94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94">
         <v>279.109375</v>
       </c>
-      <c r="C94">
+      <c r="D94">
         <v>-37.8834114074707</v>
       </c>
-      <c r="D94" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+      <c r="E94">
+        <v>-277.872171163559</v>
+      </c>
+      <c r="F94">
+        <v>51.0287036895752</v>
+      </c>
+      <c r="G94">
+        <v>505</v>
+      </c>
+      <c r="H94">
+        <v>507</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" s="1">
         <v>93</v>
       </c>
-      <c r="B95">
+      <c r="B95" t="s">
+        <v>120</v>
+      </c>
+      <c r="C95">
         <v>201.78125</v>
       </c>
-      <c r="C95">
+      <c r="D95">
         <v>-15.1946020126343</v>
       </c>
-      <c r="D95" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+      <c r="E95">
+        <v>-200.786716341972</v>
+      </c>
+      <c r="F95">
+        <v>26.3333797454834</v>
+      </c>
+      <c r="G95">
+        <v>505</v>
+      </c>
+      <c r="H95">
+        <v>508</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" s="1">
         <v>94</v>
       </c>
-      <c r="B96">
+      <c r="B96" t="s">
+        <v>121</v>
+      </c>
+      <c r="C96">
         <v>54.129035949707</v>
       </c>
-      <c r="C96">
+      <c r="D96">
         <v>-5.35495471954346</v>
       </c>
-      <c r="D96" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+      <c r="E96">
+        <v>-54.0833224281669</v>
+      </c>
+      <c r="F96">
+        <v>5.84066089987755</v>
+      </c>
+      <c r="G96">
+        <v>506</v>
+      </c>
+      <c r="H96">
+        <v>507</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>95</v>
       </c>
-      <c r="B97">
+      <c r="B97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C97">
         <v>54.129035949707</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>-5.35495471954346</v>
       </c>
-      <c r="D97" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+      <c r="E97">
+        <v>-54.0833224281669</v>
+      </c>
+      <c r="F97">
+        <v>5.84066089987755</v>
+      </c>
+      <c r="G97">
+        <v>506</v>
+      </c>
+      <c r="H97">
+        <v>507</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" s="1">
         <v>96</v>
       </c>
-      <c r="B98">
+      <c r="B98" t="s">
+        <v>122</v>
+      </c>
+      <c r="C98">
         <v>65.7419357299805</v>
       </c>
-      <c r="C98">
+      <c r="D98">
         <v>3.04294157028198</v>
       </c>
-      <c r="D98" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+      <c r="E98">
+        <v>-65.613060310483</v>
+      </c>
+      <c r="F98">
+        <v>-1.84010434150696</v>
+      </c>
+      <c r="G98">
+        <v>506</v>
+      </c>
+      <c r="H98">
+        <v>508</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" s="1">
         <v>97</v>
       </c>
-      <c r="B99">
+      <c r="B99" t="s">
+        <v>123</v>
+      </c>
+      <c r="C99">
         <v>48.6988525390625</v>
       </c>
-      <c r="C99">
+      <c r="D99">
         <v>14.1603555679321</v>
       </c>
-      <c r="D99" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+      <c r="E99">
+        <v>-48.6459537707269</v>
+      </c>
+      <c r="F99">
+        <v>-13.6578173041344</v>
+      </c>
+      <c r="G99">
+        <v>507</v>
+      </c>
+      <c r="H99">
+        <v>508</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" s="1">
         <v>98</v>
       </c>
-      <c r="B100">
+      <c r="B100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C100">
         <v>-15.9658241271973</v>
       </c>
-      <c r="C100">
+      <c r="D100">
         <v>-14.7668418884277</v>
       </c>
-      <c r="D100" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+      <c r="E100">
+        <v>16.1889219582081</v>
+      </c>
+      <c r="F100">
+        <v>16.4028927087784</v>
+      </c>
+      <c r="G100">
+        <v>507</v>
+      </c>
+      <c r="H100">
+        <v>509</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" s="1">
         <v>99</v>
       </c>
-      <c r="B101">
+      <c r="B101" t="s">
+        <v>124</v>
+      </c>
+      <c r="C101">
         <v>-15.9658241271973</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>-14.7668418884277</v>
       </c>
-      <c r="D101" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+      <c r="E101">
+        <v>16.1889219582081</v>
+      </c>
+      <c r="F101">
+        <v>16.4028927087784</v>
+      </c>
+      <c r="G101">
+        <v>507</v>
+      </c>
+      <c r="H101">
+        <v>509</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" s="1">
         <v>100</v>
       </c>
-      <c r="B102">
+      <c r="B102" t="s">
+        <v>124</v>
+      </c>
+      <c r="C102">
         <v>-15.9658241271973</v>
       </c>
-      <c r="C102">
+      <c r="D102">
         <v>-14.7668418884277</v>
       </c>
-      <c r="D102" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+      <c r="E102">
+        <v>16.1889219582081</v>
+      </c>
+      <c r="F102">
+        <v>16.4028927087784</v>
+      </c>
+      <c r="G102">
+        <v>507</v>
+      </c>
+      <c r="H102">
+        <v>509</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" s="1">
         <v>101</v>
       </c>
-      <c r="B103">
+      <c r="B103" t="s">
+        <v>124</v>
+      </c>
+      <c r="C103">
         <v>-15.9658241271973</v>
       </c>
-      <c r="C103">
+      <c r="D103">
         <v>-14.7668418884277</v>
       </c>
-      <c r="D103" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+      <c r="E103">
+        <v>16.1889219582081</v>
+      </c>
+      <c r="F103">
+        <v>16.4028927087784</v>
+      </c>
+      <c r="G103">
+        <v>507</v>
+      </c>
+      <c r="H103">
+        <v>509</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>102</v>
       </c>
-      <c r="B104">
+      <c r="B104" t="s">
+        <v>124</v>
+      </c>
+      <c r="C104">
         <v>-15.9658241271973</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>-14.7668418884277</v>
       </c>
-      <c r="D104" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+      <c r="E104">
+        <v>16.1889219582081</v>
+      </c>
+      <c r="F104">
+        <v>16.4028927087784</v>
+      </c>
+      <c r="G104">
+        <v>507</v>
+      </c>
+      <c r="H104">
+        <v>509</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" s="1">
         <v>103</v>
       </c>
-      <c r="B105">
+      <c r="B105" t="s">
+        <v>124</v>
+      </c>
+      <c r="C105">
         <v>-15.9658241271973</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>-14.7668418884277</v>
       </c>
-      <c r="D105" t="s">
-        <v>118</v>
+      <c r="E105">
+        <v>16.1889219582081</v>
+      </c>
+      <c r="F105">
+        <v>16.4028927087784</v>
+      </c>
+      <c r="G105">
+        <v>507</v>
+      </c>
+      <c r="H105">
+        <v>509</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3477,494 +5250,1019 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>66</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2">
         <v>-600</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>-77.9577026367188</v>
       </c>
-      <c r="D2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>600</v>
+      </c>
+      <c r="F2">
+        <v>121.886993408203</v>
+      </c>
+      <c r="G2">
+        <v>101</v>
+      </c>
+      <c r="H2">
+        <v>102</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3">
         <v>2800</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>193.445037841797</v>
       </c>
-      <c r="D3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-2800</v>
+      </c>
+      <c r="F3">
+        <v>162.985015869141</v>
+      </c>
+      <c r="G3">
+        <v>201</v>
+      </c>
+      <c r="H3">
+        <v>206</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4">
         <v>1920.00012207031</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>268.883911132812</v>
       </c>
-      <c r="D4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>-1920.00012207031</v>
+      </c>
+      <c r="F4">
+        <v>-13.7789154052734</v>
+      </c>
+      <c r="G4">
+        <v>202</v>
+      </c>
+      <c r="H4">
+        <v>209</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5">
         <v>920</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>166.124465942383</v>
       </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>-920</v>
+      </c>
+      <c r="F5">
+        <v>-40.0722198486328</v>
+      </c>
+      <c r="G5">
+        <v>203</v>
+      </c>
+      <c r="H5">
+        <v>208</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6">
         <v>2137.634765625</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>220.967910766602</v>
       </c>
-      <c r="D6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>-2137.634765625</v>
+      </c>
+      <c r="F6">
+        <v>40.2381439208984</v>
+      </c>
+      <c r="G6">
+        <v>204</v>
+      </c>
+      <c r="H6">
+        <v>215</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7">
         <v>198.921813964844</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-14.2097177505493</v>
       </c>
-      <c r="D7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>-198.921813964844</v>
+      </c>
+      <c r="F7">
+        <v>24.105486869812</v>
+      </c>
+      <c r="G7">
+        <v>209</v>
+      </c>
+      <c r="H7">
+        <v>210</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8">
         <v>198.921813964844</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-14.2097177505493</v>
       </c>
-      <c r="D8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>-198.921813964844</v>
+      </c>
+      <c r="F8">
+        <v>24.105486869812</v>
+      </c>
+      <c r="G8">
+        <v>209</v>
+      </c>
+      <c r="H8">
+        <v>210</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9">
         <v>198.921813964844</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-14.2097177505493</v>
       </c>
-      <c r="D9" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>-198.921813964844</v>
+      </c>
+      <c r="F9">
+        <v>24.105486869812</v>
+      </c>
+      <c r="G9">
+        <v>209</v>
+      </c>
+      <c r="H9">
+        <v>210</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10">
         <v>198.921813964844</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-14.2097177505493</v>
       </c>
-      <c r="D10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-198.921813964844</v>
+      </c>
+      <c r="F10">
+        <v>24.105486869812</v>
+      </c>
+      <c r="G10">
+        <v>209</v>
+      </c>
+      <c r="H10">
+        <v>210</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11">
         <v>198.198593139648</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>49.7862892150879</v>
       </c>
-      <c r="D11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>-198.198593139648</v>
+      </c>
+      <c r="F11">
+        <v>-39.3463907241821</v>
+      </c>
+      <c r="G11">
+        <v>213</v>
+      </c>
+      <c r="H11">
+        <v>214</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12">
         <v>198.198593139648</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>49.7862892150879</v>
       </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>-198.198593139648</v>
+      </c>
+      <c r="F12">
+        <v>-39.3463907241821</v>
+      </c>
+      <c r="G12">
+        <v>213</v>
+      </c>
+      <c r="H12">
+        <v>214</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13">
         <v>198.198593139648</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>49.7862892150879</v>
       </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>-198.198593139648</v>
+      </c>
+      <c r="F13">
+        <v>-39.3463907241821</v>
+      </c>
+      <c r="G13">
+        <v>213</v>
+      </c>
+      <c r="H13">
+        <v>214</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14">
         <v>198.198593139648</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>49.7862892150879</v>
       </c>
-      <c r="D14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>-198.198593139648</v>
+      </c>
+      <c r="F14">
+        <v>-39.3463907241821</v>
+      </c>
+      <c r="G14">
+        <v>213</v>
+      </c>
+      <c r="H14">
+        <v>214</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15">
         <v>4400</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>704.745056152344</v>
       </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>-4400</v>
+      </c>
+      <c r="F15">
+        <v>-154.031066894531</v>
+      </c>
+      <c r="G15">
+        <v>301</v>
+      </c>
+      <c r="H15">
+        <v>303</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16">
         <v>1026</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>131.446166992188</v>
       </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>-1026</v>
+      </c>
+      <c r="F16">
+        <v>-19.9685668945312</v>
+      </c>
+      <c r="G16">
+        <v>302</v>
+      </c>
+      <c r="H16">
+        <v>312</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17">
         <v>402.06689453125</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>137.387115478516</v>
       </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>-402.06689453125</v>
+      </c>
+      <c r="F17">
+        <v>-84.9336471557617</v>
+      </c>
+      <c r="G17">
+        <v>304</v>
+      </c>
+      <c r="H17">
+        <v>313</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18">
         <v>402.06689453125</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>137.387115478516</v>
       </c>
-      <c r="D18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>-402.06689453125</v>
+      </c>
+      <c r="F18">
+        <v>-84.9336471557617</v>
+      </c>
+      <c r="G18">
+        <v>304</v>
+      </c>
+      <c r="H18">
+        <v>313</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19">
         <v>125.778450012207</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-50.0237350463867</v>
       </c>
-      <c r="D19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>-125.778450012207</v>
+      </c>
+      <c r="F19">
+        <v>56.3749570846558</v>
+      </c>
+      <c r="G19">
+        <v>305</v>
+      </c>
+      <c r="H19">
+        <v>311</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20">
         <v>125.778450012207</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-50.0237350463867</v>
       </c>
-      <c r="D20" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>-125.778450012207</v>
+      </c>
+      <c r="F20">
+        <v>56.3749570846558</v>
+      </c>
+      <c r="G20">
+        <v>305</v>
+      </c>
+      <c r="H20">
+        <v>311</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21">
         <v>125.778450012207</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>-50.0237350463867</v>
       </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>-125.778450012207</v>
+      </c>
+      <c r="F21">
+        <v>56.3749570846558</v>
+      </c>
+      <c r="G21">
+        <v>305</v>
+      </c>
+      <c r="H21">
+        <v>311</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22">
         <v>321.856964111328</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>21.9822578430176</v>
       </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>-321.856964111328</v>
+      </c>
+      <c r="F22">
+        <v>2.06834983825684</v>
+      </c>
+      <c r="G22">
+        <v>305</v>
+      </c>
+      <c r="H22">
+        <v>314</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23">
         <v>321.856964111328</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>21.9822578430176</v>
       </c>
-      <c r="D23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23">
+        <v>-321.856964111328</v>
+      </c>
+      <c r="F23">
+        <v>2.06834983825684</v>
+      </c>
+      <c r="G23">
+        <v>305</v>
+      </c>
+      <c r="H23">
+        <v>314</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24">
         <v>124.587997436523</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>15.1798334121704</v>
       </c>
-      <c r="D24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24">
+        <v>-124.587997436523</v>
+      </c>
+      <c r="F24">
+        <v>-11.3256242275238</v>
+      </c>
+      <c r="G24">
+        <v>308</v>
+      </c>
+      <c r="H24">
+        <v>315</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25">
         <v>124.587997436523</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>15.1798334121704</v>
       </c>
-      <c r="D25" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25">
+        <v>-124.587997436523</v>
+      </c>
+      <c r="F25">
+        <v>-11.3256242275238</v>
+      </c>
+      <c r="G25">
+        <v>308</v>
+      </c>
+      <c r="H25">
+        <v>315</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26">
         <v>1384</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>339.579376220703</v>
       </c>
-      <c r="D26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26">
+        <v>-1384</v>
+      </c>
+      <c r="F26">
+        <v>-183.926818847656</v>
+      </c>
+      <c r="G26">
+        <v>401</v>
+      </c>
+      <c r="H26">
+        <v>410</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27">
         <v>839.999938964844</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>136.249908447266</v>
       </c>
-      <c r="D27" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27">
+        <v>-839.999938964844</v>
+      </c>
+      <c r="F27">
+        <v>-24.5829696655273</v>
+      </c>
+      <c r="G27">
+        <v>402</v>
+      </c>
+      <c r="H27">
+        <v>408</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28">
         <v>1360</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>185.293121337891</v>
       </c>
-      <c r="D28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28">
+        <v>-1360</v>
+      </c>
+      <c r="F28">
+        <v>-40.8951568603516</v>
+      </c>
+      <c r="G28">
+        <v>403</v>
+      </c>
+      <c r="H28">
+        <v>407</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29">
         <v>1360</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>252.04248046875</v>
       </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29">
+        <v>-1360</v>
+      </c>
+      <c r="F29">
+        <v>-75.0387573242188</v>
+      </c>
+      <c r="G29">
+        <v>404</v>
+      </c>
+      <c r="H29">
+        <v>405</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30">
         <v>108.081260681152</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>-32.0323944091797</v>
       </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30">
+        <v>-108.081260681152</v>
+      </c>
+      <c r="F30">
+        <v>32.9779133200645</v>
+      </c>
+      <c r="G30">
+        <v>413</v>
+      </c>
+      <c r="H30">
+        <v>414</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31">
         <v>108.081260681152</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-32.0323944091797</v>
       </c>
-      <c r="D31" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31">
+        <v>-108.081260681152</v>
+      </c>
+      <c r="F31">
+        <v>32.9779133200645</v>
+      </c>
+      <c r="G31">
+        <v>413</v>
+      </c>
+      <c r="H31">
+        <v>414</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32">
         <v>108.081260681152</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>-32.0323944091797</v>
       </c>
-      <c r="D32" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32">
+        <v>-108.081260681152</v>
+      </c>
+      <c r="F32">
+        <v>32.9779133200645</v>
+      </c>
+      <c r="G32">
+        <v>413</v>
+      </c>
+      <c r="H32">
+        <v>414</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33">
         <v>560</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>-70.361083984375</v>
       </c>
-      <c r="D33" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33">
+        <v>-560</v>
+      </c>
+      <c r="F33">
+        <v>149.204872131348</v>
+      </c>
+      <c r="G33">
+        <v>501</v>
+      </c>
+      <c r="H33">
+        <v>504</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34">
         <v>760</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>0.532488703727722</v>
       </c>
-      <c r="D34" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34">
+        <v>-760</v>
+      </c>
+      <c r="F34">
+        <v>90.961705327034</v>
+      </c>
+      <c r="G34">
+        <v>502</v>
+      </c>
+      <c r="H34">
+        <v>505</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35">
         <v>174</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>7.05032110214233</v>
       </c>
-      <c r="D35" t="s">
-        <v>139</v>
+      <c r="E35">
+        <v>-174</v>
+      </c>
+      <c r="F35">
+        <v>7.66703462600708</v>
+      </c>
+      <c r="G35">
+        <v>503</v>
+      </c>
+      <c r="H35">
+        <v>506</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
